--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FIBWI MALLORCA BASQUET PALMA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FIBWI MALLORCA BASQUET PALMA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1176</v>
+        <v>9.723400000000002</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4251</v>
+        <v>5.874500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>13.6929</v>
+        <v>3.849</v>
       </c>
       <c r="G2" t="n">
-        <v>-9.441800000000001</v>
+        <v>-5.2475</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5623</v>
+        <v>-3.8882</v>
       </c>
       <c r="I2" t="n">
-        <v>-15.0043</v>
+        <v>-1.3597</v>
       </c>
       <c r="J2" t="n">
-        <v>25.1146</v>
+        <v>5.7042</v>
       </c>
       <c r="K2" t="n">
-        <v>23.255</v>
+        <v>-0.5331000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>1.859700000000001</v>
+        <v>6.237300000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-34.5565</v>
+        <v>-10.9518</v>
       </c>
       <c r="N2" t="n">
-        <v>-17.6922</v>
+        <v>-3.354699999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-16.8639</v>
+        <v>-7.5967</v>
       </c>
       <c r="P2" t="n">
-        <v>33.0609</v>
+        <v>13.4852</v>
       </c>
       <c r="Q2" t="n">
-        <v>-36.5408</v>
+        <v>-9.5703</v>
       </c>
       <c r="R2" t="n">
-        <v>69.6024</v>
+        <v>23.0554</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4795999999999998</v>
+        <v>7.7826</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4342</v>
+        <v>6.6791</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9547</v>
+        <v>1.1036</v>
       </c>
       <c r="V2" t="n">
-        <v>-6.9809</v>
+        <v>-6.297099999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>13.4174</v>
+        <v>3.0615</v>
       </c>
       <c r="X2" t="n">
-        <v>-20.3985</v>
+        <v>-9.358599999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>14.6298</v>
+        <v>9.0616</v>
       </c>
       <c r="E3" t="n">
-        <v>8.6541</v>
+        <v>0.6597999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>5.9758</v>
+        <v>8.401999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-5.2475</v>
+        <v>-9.441800000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.8882</v>
+        <v>5.5623</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3597</v>
+        <v>-15.0043</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7042</v>
+        <v>25.1146</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5331000000000001</v>
+        <v>23.255</v>
       </c>
       <c r="L3" t="n">
-        <v>6.237300000000001</v>
+        <v>1.859700000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.9518</v>
+        <v>-34.5565</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.354699999999999</v>
+        <v>-17.6922</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.5967</v>
+        <v>-16.8639</v>
       </c>
       <c r="P3" t="n">
-        <v>13.4852</v>
+        <v>33.0609</v>
       </c>
       <c r="Q3" t="n">
-        <v>-9.5703</v>
+        <v>-36.5408</v>
       </c>
       <c r="R3" t="n">
-        <v>23.0554</v>
+        <v>69.6024</v>
       </c>
       <c r="S3" t="n">
-        <v>12.6888</v>
+        <v>-7.5764</v>
       </c>
       <c r="T3" t="n">
-        <v>9.4587</v>
+        <v>-1.3311</v>
       </c>
       <c r="U3" t="n">
-        <v>3.2302</v>
+        <v>-6.2452</v>
       </c>
       <c r="V3" t="n">
-        <v>-6.297099999999999</v>
+        <v>-6.9809</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0615</v>
+        <v>13.4174</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.358599999999999</v>
+        <v>-20.3985</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>10.3888</v>
+        <v>2.3553</v>
       </c>
       <c r="E4" t="n">
-        <v>4.012500000000001</v>
+        <v>7.171899999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>6.376200000000001</v>
+        <v>-4.817299999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>8.7699</v>
+        <v>2.213400000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>8.032400000000001</v>
+        <v>1.1688</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7381999999999999</v>
+        <v>1.0444</v>
       </c>
       <c r="J4" t="n">
-        <v>40.2721</v>
+        <v>22.7007</v>
       </c>
       <c r="K4" t="n">
-        <v>25.3727</v>
+        <v>4.3479</v>
       </c>
       <c r="L4" t="n">
-        <v>14.8985</v>
+        <v>18.3526</v>
       </c>
       <c r="M4" t="n">
-        <v>-31.5018</v>
+        <v>-20.4869</v>
       </c>
       <c r="N4" t="n">
-        <v>-17.3412</v>
+        <v>-3.179</v>
       </c>
       <c r="O4" t="n">
-        <v>-14.161</v>
+        <v>-17.3082</v>
       </c>
       <c r="P4" t="n">
-        <v>-18.7055</v>
+        <v>-4.5676</v>
       </c>
       <c r="Q4" t="n">
-        <v>-77.6499</v>
+        <v>-31.5383</v>
       </c>
       <c r="R4" t="n">
-        <v>58.9443</v>
+        <v>26.9705</v>
       </c>
       <c r="S4" t="n">
-        <v>8.4262</v>
+        <v>-0.1395999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>10.5298</v>
+        <v>0.3030999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.1035</v>
+        <v>-0.4427</v>
       </c>
       <c r="V4" t="n">
-        <v>11.8982</v>
+        <v>4.848700000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>30.8607</v>
+        <v>15.7069</v>
       </c>
       <c r="X4" t="n">
-        <v>-18.9625</v>
+        <v>-10.8582</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>L. MENUGE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8100999999999994</v>
+        <v>-3.773</v>
       </c>
       <c r="E5" t="n">
-        <v>8.2927</v>
+        <v>3.5648</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.4824</v>
+        <v>-7.3379</v>
       </c>
       <c r="G5" t="n">
-        <v>-11.9069</v>
+        <v>-4.912500000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.285</v>
+        <v>-3.592200000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-10.6215</v>
+        <v>-1.3205</v>
       </c>
       <c r="J5" t="n">
-        <v>15.8894</v>
+        <v>5.8653</v>
       </c>
       <c r="K5" t="n">
-        <v>9.7675</v>
+        <v>2.3764</v>
       </c>
       <c r="L5" t="n">
-        <v>6.121</v>
+        <v>3.4888</v>
       </c>
       <c r="M5" t="n">
-        <v>-27.7961</v>
+        <v>-10.7777</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.0524</v>
+        <v>-5.968599999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-16.7433</v>
+        <v>-4.8092</v>
       </c>
       <c r="P5" t="n">
-        <v>6.742399999999999</v>
+        <v>8.4825</v>
       </c>
       <c r="Q5" t="n">
-        <v>-35.4533</v>
+        <v>-1.74</v>
       </c>
       <c r="R5" t="n">
-        <v>42.1957</v>
+        <v>10.2225</v>
       </c>
       <c r="S5" t="n">
-        <v>26.3008</v>
+        <v>-2.4329</v>
       </c>
       <c r="T5" t="n">
-        <v>28.9131</v>
+        <v>-1.8854</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.6126</v>
+        <v>-0.5473999999999998</v>
       </c>
       <c r="V5" t="n">
-        <v>-20.3265</v>
+        <v>-4.910399999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.056200000000001</v>
+        <v>1.3252</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.2703</v>
+        <v>-6.2356</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MENUGE</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.1972</v>
+        <v>-3.8285</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2417</v>
+        <v>-4.0241</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.438800000000001</v>
+        <v>0.1955000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.912500000000001</v>
+        <v>-2.6575</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.592200000000001</v>
+        <v>0.6142</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3205</v>
+        <v>-3.2718</v>
       </c>
       <c r="J6" t="n">
-        <v>5.8653</v>
+        <v>-0.9480999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3764</v>
+        <v>1.2655</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4888</v>
+        <v>-2.2136</v>
       </c>
       <c r="M6" t="n">
-        <v>-10.7777</v>
+        <v>-1.7096</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.968599999999999</v>
+        <v>-0.6512</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.8092</v>
+        <v>-1.0582</v>
       </c>
       <c r="P6" t="n">
-        <v>8.4825</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.74</v>
+        <v>-4.7851</v>
       </c>
       <c r="R6" t="n">
-        <v>10.2225</v>
+        <v>5.2202</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.857</v>
+        <v>0.1097</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.2086</v>
+        <v>0.5791999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3516000000000001</v>
+        <v>-0.4695</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.910399999999999</v>
+        <v>-1.7156</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.2356</v>
+        <v>-2.8456</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.645799999999999</v>
+        <v>-3.8378</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.9181</v>
+        <v>-7.235299999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2723999999999999</v>
+        <v>3.3973</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6575</v>
+        <v>8.7699</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6142</v>
+        <v>8.032400000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2718</v>
+        <v>0.7381999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9480999999999999</v>
+        <v>40.2721</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2655</v>
+        <v>25.3727</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.2136</v>
+        <v>14.8985</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7096</v>
+        <v>-31.5018</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6512</v>
+        <v>-17.3412</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0582</v>
+        <v>-14.161</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>-18.7055</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.7851</v>
+        <v>-77.6499</v>
       </c>
       <c r="R7" t="n">
-        <v>5.2202</v>
+        <v>58.9443</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7074</v>
+        <v>-5.8008</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3149000000000001</v>
+        <v>-0.7182000000000003</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3926</v>
+        <v>-5.082599999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7156</v>
+        <v>11.8982</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>30.8607</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.8456</v>
+        <v>-18.9625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.338999999999999</v>
+        <v>-5.371600000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1.836799999999999</v>
+        <v>5.1299</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.1755</v>
+        <v>-10.5015</v>
       </c>
       <c r="G8" t="n">
-        <v>2.213400000000001</v>
+        <v>48.7359</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1688</v>
+        <v>26.5434</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0444</v>
+        <v>22.1924</v>
       </c>
       <c r="J8" t="n">
-        <v>22.7007</v>
+        <v>74.2878</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3479</v>
+        <v>40.9346</v>
       </c>
       <c r="L8" t="n">
-        <v>18.3526</v>
+        <v>33.3535</v>
       </c>
       <c r="M8" t="n">
-        <v>-20.4869</v>
+        <v>-25.5515</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.179</v>
+        <v>-14.3911</v>
       </c>
       <c r="O8" t="n">
-        <v>-17.3082</v>
+        <v>-11.1606</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.5676</v>
+        <v>-23.2731</v>
       </c>
       <c r="Q8" t="n">
-        <v>-31.5383</v>
+        <v>-75.6923</v>
       </c>
       <c r="R8" t="n">
-        <v>26.9705</v>
+        <v>52.4191</v>
       </c>
       <c r="S8" t="n">
-        <v>-7.8337</v>
+        <v>-16.0103</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.0327</v>
+        <v>-4.0879</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.8008</v>
+        <v>-11.9228</v>
       </c>
       <c r="V8" t="n">
-        <v>4.848700000000001</v>
+        <v>-14.8238</v>
       </c>
       <c r="W8" t="n">
-        <v>15.7069</v>
+        <v>10.6225</v>
       </c>
       <c r="X8" t="n">
-        <v>-10.8582</v>
+        <v>-25.4459</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.4158</v>
+        <v>-5.8203</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9172</v>
+        <v>-2.4758</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4984</v>
+        <v>-3.3444</v>
       </c>
       <c r="G9" t="n">
         <v>-7.2579</v>
@@ -1156,13 +1156,13 @@
         <v>2.8275</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4919</v>
+        <v>1.0874</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0574</v>
+        <v>1.4986</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5655</v>
+        <v>-0.4111</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2599</v>
@@ -1189,13 +1189,13 @@
         <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>-14.5211</v>
+        <v>-12.5383</v>
       </c>
       <c r="E10" t="n">
-        <v>-14.0301</v>
+        <v>-12.217</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4910999999999998</v>
+        <v>-0.3214999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-8.7921</v>
@@ -1234,13 +1234,13 @@
         <v>12.8327</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7844</v>
+        <v>0.1988000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8809000000000002</v>
+        <v>0.9325000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9037000000000001</v>
+        <v>-0.734</v>
       </c>
       <c r="V10" t="n">
         <v>-3.727</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.4319</v>
+        <v>-16.1497</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.801400000000001</v>
+        <v>-16.4559</v>
       </c>
       <c r="F11" t="n">
-        <v>-13.6303</v>
+        <v>0.3067999999999995</v>
       </c>
       <c r="G11" t="n">
-        <v>48.7359</v>
+        <v>-31.6736</v>
       </c>
       <c r="H11" t="n">
-        <v>26.5434</v>
+        <v>-11.631</v>
       </c>
       <c r="I11" t="n">
-        <v>22.1924</v>
+        <v>-20.0423</v>
       </c>
       <c r="J11" t="n">
-        <v>74.2878</v>
+        <v>5.744</v>
       </c>
       <c r="K11" t="n">
-        <v>40.9346</v>
+        <v>3.2199</v>
       </c>
       <c r="L11" t="n">
-        <v>33.3535</v>
+        <v>2.5239</v>
       </c>
       <c r="M11" t="n">
-        <v>-25.5515</v>
+        <v>-37.4174</v>
       </c>
       <c r="N11" t="n">
-        <v>-14.3911</v>
+        <v>-14.8514</v>
       </c>
       <c r="O11" t="n">
-        <v>-11.1606</v>
+        <v>-22.566</v>
       </c>
       <c r="P11" t="n">
-        <v>-23.2731</v>
+        <v>12.6153</v>
       </c>
       <c r="Q11" t="n">
-        <v>-75.6923</v>
+        <v>-55.0289</v>
       </c>
       <c r="R11" t="n">
-        <v>52.4191</v>
+        <v>67.6448</v>
       </c>
       <c r="S11" t="n">
-        <v>-27.0708</v>
+        <v>-18.4109</v>
       </c>
       <c r="T11" t="n">
-        <v>-12.019</v>
+        <v>-6.0841</v>
       </c>
       <c r="U11" t="n">
-        <v>-15.0516</v>
+        <v>-12.3269</v>
       </c>
       <c r="V11" t="n">
-        <v>-14.8238</v>
+        <v>21.3191</v>
       </c>
       <c r="W11" t="n">
-        <v>10.6225</v>
+        <v>38.913</v>
       </c>
       <c r="X11" t="n">
-        <v>-25.4459</v>
+        <v>-17.5934</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>-31.3177</v>
+        <v>-17.7668</v>
       </c>
       <c r="E12" t="n">
-        <v>-21.1538</v>
+        <v>-3.757399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.164</v>
+        <v>-14.009</v>
       </c>
       <c r="G12" t="n">
-        <v>-31.6736</v>
+        <v>6.4927</v>
       </c>
       <c r="H12" t="n">
-        <v>-11.631</v>
+        <v>-1.210400000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-20.0423</v>
+        <v>7.7033</v>
       </c>
       <c r="J12" t="n">
-        <v>5.744</v>
+        <v>42.3715</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2199</v>
+        <v>21.237</v>
       </c>
       <c r="L12" t="n">
-        <v>2.5239</v>
+        <v>21.1338</v>
       </c>
       <c r="M12" t="n">
-        <v>-37.4174</v>
+        <v>-35.8783</v>
       </c>
       <c r="N12" t="n">
-        <v>-14.8514</v>
+        <v>-22.4477</v>
       </c>
       <c r="O12" t="n">
-        <v>-22.566</v>
+        <v>-13.4309</v>
       </c>
       <c r="P12" t="n">
-        <v>12.6153</v>
+        <v>-19.5759</v>
       </c>
       <c r="Q12" t="n">
-        <v>-55.0289</v>
+        <v>-75.9097</v>
       </c>
       <c r="R12" t="n">
-        <v>67.6448</v>
+        <v>56.3343</v>
       </c>
       <c r="S12" t="n">
-        <v>-33.5785</v>
+        <v>-11.6605</v>
       </c>
       <c r="T12" t="n">
-        <v>-10.781</v>
+        <v>-2.7215</v>
       </c>
       <c r="U12" t="n">
-        <v>-22.7969</v>
+        <v>-8.938700000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>21.3191</v>
+        <v>6.977</v>
       </c>
       <c r="W12" t="n">
-        <v>38.913</v>
+        <v>32.5032</v>
       </c>
       <c r="X12" t="n">
-        <v>-17.5934</v>
+        <v>-25.5262</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>-32.83580000000001</v>
+        <v>-20.3817</v>
       </c>
       <c r="E13" t="n">
-        <v>-30.3597</v>
+        <v>-24.0045</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4759</v>
+        <v>3.6227</v>
       </c>
       <c r="G13" t="n">
         <v>-16.435</v>
@@ -1468,13 +1468,13 @@
         <v>55.4644</v>
       </c>
       <c r="S13" t="n">
-        <v>-22.8568</v>
+        <v>-10.4028</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.177300000000001</v>
+        <v>-1.8213</v>
       </c>
       <c r="U13" t="n">
-        <v>-14.6796</v>
+        <v>-8.5814</v>
       </c>
       <c r="V13" t="n">
         <v>-9.2042</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>-39.0078</v>
+        <v>-21.0404</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.1793</v>
+        <v>-11.8889</v>
       </c>
       <c r="F14" t="n">
-        <v>-21.8285</v>
+        <v>-9.1517</v>
       </c>
       <c r="G14" t="n">
-        <v>6.4927</v>
+        <v>-11.9069</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.210400000000001</v>
+        <v>-1.285</v>
       </c>
       <c r="I14" t="n">
-        <v>7.7033</v>
+        <v>-10.6215</v>
       </c>
       <c r="J14" t="n">
-        <v>42.3715</v>
+        <v>15.8894</v>
       </c>
       <c r="K14" t="n">
-        <v>21.237</v>
+        <v>9.7675</v>
       </c>
       <c r="L14" t="n">
-        <v>21.1338</v>
+        <v>6.121</v>
       </c>
       <c r="M14" t="n">
-        <v>-35.8783</v>
+        <v>-27.7961</v>
       </c>
       <c r="N14" t="n">
-        <v>-22.4477</v>
+        <v>-11.0524</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.4309</v>
+        <v>-16.7433</v>
       </c>
       <c r="P14" t="n">
-        <v>-19.5759</v>
+        <v>6.742399999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-75.9097</v>
+        <v>-35.4533</v>
       </c>
       <c r="R14" t="n">
-        <v>56.3343</v>
+        <v>42.1957</v>
       </c>
       <c r="S14" t="n">
-        <v>-32.9014</v>
+        <v>4.4502</v>
       </c>
       <c r="T14" t="n">
-        <v>-16.1429</v>
+        <v>8.7315</v>
       </c>
       <c r="U14" t="n">
-        <v>-16.7583</v>
+        <v>-4.2818</v>
       </c>
       <c r="V14" t="n">
-        <v>6.977</v>
+        <v>-20.3265</v>
       </c>
       <c r="W14" t="n">
-        <v>32.5032</v>
+        <v>-1.056200000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-25.5262</v>
+        <v>-19.2703</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>-71.24210000000001</v>
+        <v>-57.7263</v>
       </c>
       <c r="E15" t="n">
-        <v>-38.0394</v>
+        <v>-31.2076</v>
       </c>
       <c r="F15" t="n">
-        <v>-33.2027</v>
+        <v>-26.5186</v>
       </c>
       <c r="G15" t="n">
         <v>-42.1545</v>
@@ -1624,13 +1624,13 @@
         <v>50.244</v>
       </c>
       <c r="S15" t="n">
-        <v>-25.432</v>
+        <v>-11.9163</v>
       </c>
       <c r="T15" t="n">
-        <v>-9.718</v>
+        <v>-2.8862</v>
       </c>
       <c r="U15" t="n">
-        <v>-15.7141</v>
+        <v>-9.0303</v>
       </c>
       <c r="V15" t="n">
         <v>-25.8414</v>
@@ -1657,16 +1657,16 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-182.0079</v>
+        <v>-147.0941</v>
       </c>
       <c r="E16" t="n">
-        <v>-101.9361</v>
+        <v>-90.8656</v>
       </c>
       <c r="F16" t="n">
-        <v>-80.0703</v>
+        <v>-56.22860000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-74.26739999999999</v>
+        <v>-74.26739999999998</v>
       </c>
       <c r="H16" t="n">
         <v>2.478599999999998</v>
@@ -1681,7 +1681,7 @@
         <v>148.7066</v>
       </c>
       <c r="L16" t="n">
-        <v>86.568</v>
+        <v>86.56799999999998</v>
       </c>
       <c r="M16" t="n">
         <v>-309.5438</v>
@@ -1702,16 +1702,16 @@
         <v>533.9778</v>
       </c>
       <c r="S16" t="n">
-        <v>-105.6347</v>
+        <v>-70.7218</v>
       </c>
       <c r="T16" t="n">
-        <v>-13.88209999999999</v>
+        <v>-2.811700000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-91.7521</v>
+        <v>-67.91080000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-51.0438</v>
+        <v>-51.04379999999999</v>
       </c>
       <c r="W16" t="n">
         <v>161.7093</v>
